--- a/#US_anonymized.xlsx
+++ b/#US_anonymized.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10831,7 +10831,7 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10915,7 +10915,7 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11000,7 +11000,7 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16676,7 +16676,7 @@
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16718,7 +16718,7 @@
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16760,7 +16760,7 @@
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21681,7 +21681,7 @@
       </c>
       <c r="J629" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21724,7 +21724,7 @@
       </c>
       <c r="J630" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21766,7 +21766,7 @@
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21809,7 +21809,7 @@
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21851,7 +21851,7 @@
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26269,7 +26269,7 @@
       </c>
       <c r="J764" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26312,7 +26312,7 @@
       </c>
       <c r="J765" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="J766" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26399,7 +26399,7 @@
       </c>
       <c r="J767" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31973,7 +31973,7 @@
       </c>
       <c r="J935" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32013,7 +32013,7 @@
       </c>
       <c r="J936" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32055,7 +32055,7 @@
       </c>
       <c r="J937" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32095,7 +32095,7 @@
       </c>
       <c r="J938" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32135,7 +32135,7 @@
       </c>
       <c r="J939" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32174,7 +32174,7 @@
       </c>
       <c r="J940" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
